--- a/outputs/abilityfinder-remediation-2026-07-22/AbilityFinder_Remediation_Tracker_2026-07-22.xlsx
+++ b/outputs/abilityfinder-remediation-2026-07-22/AbilityFinder_Remediation_Tracker_2026-07-22.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9e32dc2c91e04271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remediation Tracker" sheetId="2" r:id="R012a02adb4ed456e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Evidence" sheetId="3" r:id="R04d31c9ba6034320"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R37eb709ed6024c25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remediation Tracker" sheetId="2" r:id="R847a688803fb4d0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Evidence" sheetId="3" r:id="R941211297b81449b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -58,8 +58,51 @@
       <x:color rgb="FF1F5A50"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF294645"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1C6158"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1C6158"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF294645"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1C6158"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF24566A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1C6158"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF294645"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -96,8 +139,123 @@
         <x:fgColor rgb="FFFBF8F2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF8F5EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE3F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF8F5EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE3F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F1F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFBE7E2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF8F5EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE3F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F1F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFBE7E2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF8F5EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE3F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F1F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFBE7E2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF8F5EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE3F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F1F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFBE7E2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -113,11 +271,25 @@
         <x:color rgb="FFD7D4CC"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8D4CB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD8D4CB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8D4CB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8D4CB"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="142">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -185,6 +357,308 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="29" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="29" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -197,7 +671,7 @@
         <x:color rgb="FF1F5A50"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE6F1EC"/>
         </x:patternFill>
       </x:fill>
@@ -208,7 +682,7 @@
         <x:color rgb="FF7A5312"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1D6"/>
         </x:patternFill>
       </x:fill>
@@ -219,7 +693,7 @@
         <x:color rgb="FF24566B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE8F1F5"/>
         </x:patternFill>
       </x:fill>
@@ -434,7 +908,7 @@
     <x:row r="1" ht="52" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>AbilityFinder remediation tracker
-Recommended safety batches 1–3 • updated 2026-07-22 • no commit, push, or deployment</x:v>
+Safety batches 1–6 • updated 2026-07-22 • batches 1–3 deployed; batches 4–6 local</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="52" customHeight="1"/>
@@ -456,11 +930,10 @@
         <x:v>Completed</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:f>COUNTIF('Remediation Tracker'!$F$5:$F$22,A5)</x:f>
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="19" t="str">
-        <x:v>NO-GO remains in effect. Three batches removed several unsupported “ready” verdicts and six high-risk factual defects, but unresolved matcher, accessibility, security, privacy, intake-state, and assistant-grounding blockers remain.</x:v>
+        <x:v>NO-GO remains. Batches 1–3 are live; batches 4–6 are local. SEC-01 needs deployment plus Always Use HTTPS. PRIV-01 needs deployment plus Web Analytics disabled. Intake-state, matcher, and broader data blockers remain.</x:v>
       </x:c>
       <x:c r="E5" s="19"/>
       <x:c r="F5" s="19"/>
@@ -470,7 +943,6 @@
         <x:v>Mitigated — follow-up required</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:f>COUNTIF('Remediation Tracker'!$F$5:$F$22,A6)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="19"/>
@@ -482,8 +954,7 @@
         <x:v>In progress</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:f>COUNTIF('Remediation Tracker'!$F$5:$F$22,A7)</x:f>
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D7" s="19"/>
       <x:c r="E7" s="19"/>
@@ -511,13 +982,13 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="20" t="str">
-        <x:v>17 findings completed/mitigated; systematic test gap advanced</x:v>
+        <x:v>21 findings completed/mitigated; 3 in progress</x:v>
       </x:c>
       <x:c r="B11" s="20" t="str">
-        <x:v>29/29 passed</x:v>
+        <x:v>44/44 passed</x:v>
       </x:c>
       <x:c r="C11" s="20" t="str">
-        <x:v>32/32 passed</x:v>
+        <x:v>33/33 passed</x:v>
       </x:c>
       <x:c r="D11" s="20" t="str">
         <x:v>250,000 models; 0 exceptions</x:v>
@@ -526,7 +997,7 @@
         <x:v>Passed</x:v>
       </x:c>
       <x:c r="F11" s="20" t="str">
-        <x:v>Not deployed</x:v>
+        <x:v>Batches 1–3 live; batches 4–6 local</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="34" customHeight="1">
@@ -598,7 +1069,7 @@
     <x:row r="1" ht="52" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>Remediation Tracker
-Status is evidence-based: completed, mitigated with follow-up, or in progress</x:v>
+Batches 1–3 deployed; batches 4–6 are local and awaiting release approval</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="52" customHeight="1"/>
@@ -1011,7 +1482,7 @@
         <x:v>Exact browser assertions cover the model, homepage, totals, and generated guide; 7/7 focused and 28/28 full browser tests passed.</x:v>
       </x:c>
       <x:c r="J14" s="13" t="str">
-        <x:v>Production remains unchanged until an owner-approved release; continue the broader tax-credit content review before adding any estimate.</x:v>
+        <x:v>Deployed in commit 68b8dfc. Continue the broader tax-credit content review before adding any estimate.</x:v>
       </x:c>
       <x:c r="K14" s="13" t="str">
         <x:v>public/data.js; public/app.js; public/stateManager.js; public/guides/dtc.html; src/benefits-context.js; e2e/matcher-safety.spec.js</x:v>
@@ -1322,6 +1793,234 @@
       </x:c>
       <x:c r="L22" s="13" t="str">
         <x:v>https://www.alberta.ca/aish-apply-for-federal-disability-supports</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="81" customHeight="1">
+      <x:c r="A23" s="37" t="str">
+        <x:v>AI-01</x:v>
+      </x:c>
+      <x:c r="B23" s="37" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C23" s="37" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="D23" s="37" t="str">
+        <x:v>Reliability / Data accuracy</x:v>
+      </x:c>
+      <x:c r="E23" s="37" t="str">
+        <x:v>Assistant grounding</x:v>
+      </x:c>
+      <x:c r="F23" s="40" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="G23" s="37" t="str">
+        <x:v>Redacted all catalogue and detail narrative amounts, percentages, age limits, cutoffs, and embedded contacts. The generator now fails closed, while verified form and contact facts are passed as explicit typed fields.</x:v>
+      </x:c>
+      <x:c r="H23" s="37" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="I23" s="37" t="str">
+        <x:v>Six assistant regressions passed, including a captured Worker system prompt; npm test passed 35/35, npm run gen:context passed, the full browser suite passed 32/32, and the Wrangler dry-run passed.</x:v>
+      </x:c>
+      <x:c r="J23" s="37" t="str">
+        <x:v>After an owner-approved release, run bounded synthetic production prompts for amount, eligibility, deadline, and prompt-injection requests. Monitor over-redaction and refusal quality without widening the assistant role.</x:v>
+      </x:c>
+      <x:c r="K23" s="37" t="str">
+        <x:v>scripts/benefits-context-safety.js; scripts/gen-benefits-context.js; src/benefits-context.js; src/index.js; test/assistant-grounding.test.js</x:v>
+      </x:c>
+      <x:c r="L23" s="37" t="str">
+        <x:v>Not applicable — assistant safety/control finding; reviewed program facts remain in guides and typed fields</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="81" customHeight="1">
+      <x:c r="A24" s="38" t="str">
+        <x:v>AI-02</x:v>
+      </x:c>
+      <x:c r="B24" s="38" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C24" s="38" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D24" s="38" t="str">
+        <x:v>Reliability</x:v>
+      </x:c>
+      <x:c r="E24" s="38" t="str">
+        <x:v>Assistant province scope</x:v>
+      </x:c>
+      <x:c r="F24" s="40" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="G24" s="38" t="str">
+        <x:v>Generated the assistant scope from BC_ENABLED. The Worker now explicitly covers Alberta, British Columbia, and federal programs, and qualifies unsupported provinces without discarding potentially applicable federal information.</x:v>
+      </x:c>
+      <x:c r="H24" s="38" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="I24" s="38" t="str">
+        <x:v>A VM-loaded Worker test captured the actual system prompt and confirmed Alberta/BC/federal scope, unsupported-province handling, and redacted catalogue text; all 35 unit and 32 browser tests passed.</x:v>
+      </x:c>
+      <x:c r="J24" s="38" t="str">
+        <x:v>After release, use a small synthetic prompt matrix for Alberta, BC, federal, and unsupported provinces plus follow-ups. Keep production checks bounded to preserve the Workers AI free allocation.</x:v>
+      </x:c>
+      <x:c r="K24" s="38" t="str">
+        <x:v>scripts/gen-benefits-context.js; src/benefits-context.js; src/index.js; test/assistant-grounding.test.js</x:v>
+      </x:c>
+      <x:c r="L24" s="38" t="str">
+        <x:v>Not applicable — product and Worker contract finding</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="112" customHeight="1">
+      <x:c r="A25" s="118" t="str">
+        <x:v>A11Y-01</x:v>
+      </x:c>
+      <x:c r="B25" s="118" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C25" s="118" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="D25" s="118" t="str">
+        <x:v>Accessibility</x:v>
+      </x:c>
+      <x:c r="E25" s="118" t="str">
+        <x:v>Wizard choice semantics and focus</x:v>
+      </x:c>
+      <x:c r="F25" s="123" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="G25" s="118" t="str">
+        <x:v>Replaced custom choice buttons with native radio/checkbox inputs inside fieldset/legend groups. Same-question multi-select changes update in place and retain focus; deliberate navigation focuses the next question heading. Added visible and forced-colours focus treatment.</x:v>
+      </x:c>
+      <x:c r="H25" s="118" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="I25" s="118" t="str">
+        <x:v>Dedicated Chromium test verifies role/state/group semantics, unique radio grouping, checkbox focus persistence, visual selected state, Next enablement, and next-heading focus. Final full browser suite passed 33/33.</x:v>
+      </x:c>
+      <x:c r="J25" s="118" t="str">
+        <x:v>Validate with VoiceOver, NVDA and TalkBack plus switch/voice input and real disabled users before making any conformance claim.</x:v>
+      </x:c>
+      <x:c r="K25" s="118" t="str">
+        <x:v>public/app.js; public/styles.css; public/index.html; e2e/wizard-accessibility.spec.js; e2e/persistence.spec.js; e2e/bc-live.spec.js</x:v>
+      </x:c>
+      <x:c r="L25" s="118" t="str">
+        <x:v>https://www.w3.org/TR/WCAG22/#name-role-value; https://www.w3.org/TR/WCAG22/#focus-order</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="112" customHeight="1">
+      <x:c r="A26" s="120" t="str">
+        <x:v>SEC-01</x:v>
+      </x:c>
+      <x:c r="B26" s="120" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C26" s="120" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="D26" s="120" t="str">
+        <x:v>Security</x:v>
+      </x:c>
+      <x:c r="E26" s="120" t="str">
+        <x:v>HTTP redirect and HSTS</x:v>
+      </x:c>
+      <x:c r="F26" s="125" t="str">
+        <x:v>In progress</x:v>
+      </x:c>
+      <x:c r="G26" s="120" t="str">
+        <x:v>Added six-month HSTS to static and Worker HTTPS responses and same-path 308 redirects for canonical-host HTTP requests that reach the Worker. Kept includeSubDomains/preload off and avoided run_worker_first so static traffic stays assets-first on Workers Free.</x:v>
+      </x:c>
+      <x:c r="H26" s="120" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="I26" s="120" t="str">
+        <x:v>Four Worker/header contract tests passed; Wrangler dry-run packaged 110 assets with expected bindings. Production header recheck still observed HTTP 200 for root, canonical generated guide and asset, with no HSTS because the batch and zone setting are not live.</x:v>
+      </x:c>
+      <x:c r="J26" s="120" t="str">
+        <x:v>Deploy the batch and enable Cloudflare Always Use HTTPS. Verify HTTP root, generated guide, asset and API redirects plus HSTS on every HTTPS static/API response. Inventory subdomains before any stronger HSTS policy.</x:v>
+      </x:c>
+      <x:c r="K26" s="120" t="str">
+        <x:v>public/_headers; src/index.js; test/worker-transport.test.js</x:v>
+      </x:c>
+      <x:c r="L26" s="120" t="str">
+        <x:v>https://developers.cloudflare.com/ssl/edge-certificates/additional-options/always-use-https/; https://developers.cloudflare.com/use-cases/solutions/encrypt-all-keep-site-secure/; https://developers.cloudflare.com/workers/static-assets/routing/worker-script/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="122" customHeight="1">
+      <x:c r="A27" s="118" t="str">
+        <x:v>PRIV-01</x:v>
+      </x:c>
+      <x:c r="B27" s="118" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C27" s="118" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D27" s="118" t="str">
+        <x:v>Privacy / Maintainability</x:v>
+      </x:c>
+      <x:c r="E27" s="118" t="str">
+        <x:v>Analytics, CSP, and privacy representations</x:v>
+      </x:c>
+      <x:c r="F27" s="125" t="str">
+        <x:v>In progress</x:v>
+      </x:c>
+      <x:c r="G27" s="118" t="str">
+        <x:v>Removed the explicit Cloudflare Web Analytics beacon from the app shell, generator, and all 84 generated guide HTML surfaces. Restored self-only script/connect CSP. Updated privacy, partner, and impact copy to the no-analytics boundary; advanced browser assets to v48.</x:v>
+      </x:c>
+      <x:c r="H27" s="118" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="I27" s="118" t="str">
+        <x:v>Repository privacy contract scans source, CSP, generator, and all generated guides. Browser privacy journey allows only same-origin application requests. Local Wrangler returned strict self-only CSP; full unit and browser suites passed.</x:v>
+      </x:c>
+      <x:c r="J27" s="118" t="str">
+        <x:v>Disable the Web Analytics site in the Cloudflare dashboard, deploy, and verify no edge-injected beacon, analytics request, or CSP exception on the app and representative guides.</x:v>
+      </x:c>
+      <x:c r="K27" s="118" t="str">
+        <x:v>public/index.html; public/_headers; public/app.js; public/i18n.js; public/styles.css; scripts/gen-guide-pages.js; public/guides/*.html; test/privacy-contract.test.js; e2e/persistence.spec.js</x:v>
+      </x:c>
+      <x:c r="L27" s="118" t="str">
+        <x:v>https://developers.cloudflare.com/web-analytics/get-started/; https://developers.cloudflare.com/workers/static-assets/headers/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="122" customHeight="1">
+      <x:c r="A28" s="120" t="str">
+        <x:v>SEC-02</x:v>
+      </x:c>
+      <x:c r="B28" s="120" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C28" s="120" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D28" s="120" t="str">
+        <x:v>Security / Reliability</x:v>
+      </x:c>
+      <x:c r="E28" s="120" t="str">
+        <x:v>Assistant and feedback API origin boundary</x:v>
+      </x:c>
+      <x:c r="F28" s="123" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="G28" s="120" t="str">
+        <x:v>Removed wildcard CORS. Require an exact parseable same-origin Origin before method handling, rate limiting, AI, or email binding access. Missing, null, malformed, path-bearing, and hostile origins fail with 403/no-store; same-origin preflight returns 204 without CORS permission headers.</x:v>
+      </x:c>
+      <x:c r="H28" s="120" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="I28" s="120" t="str">
+        <x:v>Four focused Worker contracts passed. Local Wrangler reproduced same-origin 204, hostile 403, missing-origin 403, and normal same-origin request validation without real AI or email calls. Full suite passed 44/44.</x:v>
+      </x:c>
+      <x:c r="J28" s="120" t="str">
+        <x:v>Deploy and repeat the same-origin/hostile/missing/malformed contracts at the production edge. Keep the existing per-IP limiter because non-browser clients can forge Origin.</x:v>
+      </x:c>
+      <x:c r="K28" s="120" t="str">
+        <x:v>src/index.js; test/worker-transport.test.js; test/assistant-grounding.test.js</x:v>
+      </x:c>
+      <x:c r="L28" s="120" t="str">
+        <x:v>https://developers.cloudflare.com/cache/cache-security/cors/; https://developers.cloudflare.com/workers/best-practices/workers-best-practices/</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1333,9 +2032,18 @@
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Mitigated"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="In progress"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="F5:F22">
       <x:formula1>"Completed,Mitigated — follow-up required,In progress,Not started"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F23:F24">
+      <x:formula1>"Completed,Mitigated — follow-up required,In progress"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F25:F26">
+      <x:formula1>"Completed,Mitigated — follow-up required,In progress"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F27:F28">
+      <x:formula1>"Completed,Mitigated — follow-up required,In progress"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1357,7 +2065,7 @@
     <x:row r="1" ht="52" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>Run Evidence
-Commands and checks observed after the remediation changes</x:v>
+Release evidence for batches 1–3 and local verification for batches 4–6</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="52" customHeight="1"/>
@@ -1658,6 +2366,446 @@
         <x:v>No commit or push performed</x:v>
       </x:c>
       <x:c r="F18" s="13" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="52.5" customHeight="1">
+      <x:c r="A19" s="37" t="str">
+        <x:v>Release commit and production deployment</x:v>
+      </x:c>
+      <x:c r="B19" s="43" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C19" s="37" t="str">
+        <x:v>Commit 68b8dfc64909b2435698f26886763f611ac61e89 pushed to origin/main; Cloudflare version 1ee35dbc-8547-4023-b65a-cbd1f9a6b755 deployed; production smoke passed.</x:v>
+      </x:c>
+      <x:c r="D19" s="37" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E19" s="37" t="str">
+        <x:v>Batches 1–3 only; abilityfinder.ca</x:v>
+      </x:c>
+      <x:c r="F19" s="37" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="52.5" customHeight="1">
+      <x:c r="A20" s="38" t="str">
+        <x:v>Assistant grounding generator</x:v>
+      </x:c>
+      <x:c r="B20" s="43" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C20" s="38" t="str">
+        <x:v>84 context entries and 151 monitored links generated; prohibited narrative facts fail closed; verified contact and practitioner-form facts remain typed separately.</x:v>
+      </x:c>
+      <x:c r="D20" s="38" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E20" s="38" t="str">
+        <x:v>Batch 4; local repository; not deployed</x:v>
+      </x:c>
+      <x:c r="F20" s="38" t="str">
+        <x:v>Code-confirmed / Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="52.5" customHeight="1">
+      <x:c r="A21" s="37" t="str">
+        <x:v>Assistant Worker contract tests</x:v>
+      </x:c>
+      <x:c r="B21" s="43" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C21" s="37" t="str">
+        <x:v>6/6: redaction fixtures, fail-closed assertion, generated-content safety, BC-derived scope, captured system prompt, and fragmented numeric SSE token handling.</x:v>
+      </x:c>
+      <x:c r="D21" s="37" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E21" s="37" t="str">
+        <x:v>Batch 4; local Worker mock</x:v>
+      </x:c>
+      <x:c r="F21" s="37" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="52.5" customHeight="1">
+      <x:c r="A22" s="38" t="str">
+        <x:v>npm test — assistant batch</x:v>
+      </x:c>
+      <x:c r="B22" s="43" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C22" s="38" t="str">
+        <x:v>35/35; 0 failed; 0 skipped</x:v>
+      </x:c>
+      <x:c r="D22" s="38" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E22" s="38" t="str">
+        <x:v>Batch 4; Node test runner</x:v>
+      </x:c>
+      <x:c r="F22" s="38" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="52.5" customHeight="1">
+      <x:c r="A23" s="37" t="str">
+        <x:v>npm run test:e2e — assistant batch</x:v>
+      </x:c>
+      <x:c r="B23" s="43" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C23" s="37" t="str">
+        <x:v>Final clean regression 32/32</x:v>
+      </x:c>
+      <x:c r="D23" s="37" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E23" s="37" t="str">
+        <x:v>Batch 4; Chromium; local static server</x:v>
+      </x:c>
+      <x:c r="F23" s="37" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="52.5" customHeight="1">
+      <x:c r="A24" s="38" t="str">
+        <x:v>Wrangler dry-run — assistant batch</x:v>
+      </x:c>
+      <x:c r="B24" s="43" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C24" s="38" t="str">
+        <x:v>110 assets; 199.30 KiB / 51.81 KiB gzip; expected KV, email, AI, rate-limit, and asset bindings.</x:v>
+      </x:c>
+      <x:c r="D24" s="38" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E24" s="38" t="str">
+        <x:v>Batch 4; no deployment performed</x:v>
+      </x:c>
+      <x:c r="F24" s="38" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64" customHeight="1">
+      <x:c r="A25" s="118" t="str">
+        <x:v>Wizard accessibility contract</x:v>
+      </x:c>
+      <x:c r="B25" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C25" s="118" t="str">
+        <x:v>1/1 focused browser journey: native radio/checkbox semantics, fieldset/legend, focus persistence, selected styling, Next state, and focus transfer.</x:v>
+      </x:c>
+      <x:c r="D25" s="118" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E25" s="118" t="str">
+        <x:v>Batch 5; Chromium; local static server</x:v>
+      </x:c>
+      <x:c r="F25" s="118" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="64" customHeight="1">
+      <x:c r="A26" s="120" t="str">
+        <x:v>Worker transport contract</x:v>
+      </x:c>
+      <x:c r="B26" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C26" s="120" t="str">
+        <x:v>4/4: canonical HTTP redirect, HTTPS HSTS/static/API body preservation, local HTTP behavior, and repository policy invariants.</x:v>
+      </x:c>
+      <x:c r="D26" s="120" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E26" s="120" t="str">
+        <x:v>Batch 5; Node Worker mock</x:v>
+      </x:c>
+      <x:c r="F26" s="120" t="str">
+        <x:v>Observed / Code-confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64" customHeight="1">
+      <x:c r="A27" s="118" t="str">
+        <x:v>npm test — batch 5</x:v>
+      </x:c>
+      <x:c r="B27" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C27" s="118" t="str">
+        <x:v>39/39; 0 failed; 0 skipped</x:v>
+      </x:c>
+      <x:c r="D27" s="118" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E27" s="118" t="str">
+        <x:v>Batch 5; Node test runner</x:v>
+      </x:c>
+      <x:c r="F27" s="118" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="64" customHeight="1">
+      <x:c r="A28" s="120" t="str">
+        <x:v>npm run test:e2e — batch 5</x:v>
+      </x:c>
+      <x:c r="B28" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C28" s="120" t="str">
+        <x:v>Final clean regression 33/33 after updating legacy role selectors to the native control contract.</x:v>
+      </x:c>
+      <x:c r="D28" s="120" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E28" s="120" t="str">
+        <x:v>Batch 5; Chromium; local static server</x:v>
+      </x:c>
+      <x:c r="F28" s="120" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="64" customHeight="1">
+      <x:c r="A29" s="118" t="str">
+        <x:v>Wrangler dry-run — batch 5</x:v>
+      </x:c>
+      <x:c r="B29" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C29" s="118" t="str">
+        <x:v>Wrangler 4.112.0; 110 assets; 200.33 KiB / 52.10 KiB gzip; expected KV, email, AI, rate-limit, and asset bindings.</x:v>
+      </x:c>
+      <x:c r="D29" s="118" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E29" s="118" t="str">
+        <x:v>Batch 5; no deployment performed</x:v>
+      </x:c>
+      <x:c r="F29" s="118" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="64" customHeight="1">
+      <x:c r="A30" s="120" t="str">
+        <x:v>Production transport recheck</x:v>
+      </x:c>
+      <x:c r="B30" s="140" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="C30" s="120" t="str">
+        <x:v>HTTP root, canonical generated guide and app.js returned 200; HTTP API returned its normal method response; HTTPS root, guide and link-health lacked HSTS. Local change is not deployed and Always Use HTTPS is not enabled.</x:v>
+      </x:c>
+      <x:c r="D30" s="120" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E30" s="120" t="str">
+        <x:v>abilityfinder.ca; safe HEAD requests; Cloudflare SEA edge</x:v>
+      </x:c>
+      <x:c r="F30" s="120" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="64" customHeight="1">
+      <x:c r="A31" s="118" t="str">
+        <x:v>git diff --check — batches 4–5</x:v>
+      </x:c>
+      <x:c r="B31" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C31" s="118" t="str">
+        <x:v>No whitespace errors.</x:v>
+      </x:c>
+      <x:c r="D31" s="118" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E31" s="118" t="str">
+        <x:v>Local repository; no commit, push, or deployment performed</x:v>
+      </x:c>
+      <x:c r="F31" s="118" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="72" customHeight="1">
+      <x:c r="A32" s="120" t="str">
+        <x:v>npm run gen:guides — batch 6</x:v>
+      </x:c>
+      <x:c r="B32" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C32" s="120" t="str">
+        <x:v>Regenerated 83 benefit pages plus guide index and sitemap; local-supports correctly remained dynamic.</x:v>
+      </x:c>
+      <x:c r="D32" s="120" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E32" s="120" t="str">
+        <x:v>Batch 6; generated-source workflow</x:v>
+      </x:c>
+      <x:c r="F32" s="120" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="72" customHeight="1">
+      <x:c r="A33" s="118" t="str">
+        <x:v>No-analytics repository contract</x:v>
+      </x:c>
+      <x:c r="B33" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C33" s="118" t="str">
+        <x:v>App shell, self-only CSP, guide generator, privacy copy, and all 84 generated guide HTML files contain no analytics beacon or Cloudflare Insights allowlist.</x:v>
+      </x:c>
+      <x:c r="D33" s="118" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E33" s="118" t="str">
+        <x:v>Batch 6; Node repository contract</x:v>
+      </x:c>
+      <x:c r="F33" s="118" t="str">
+        <x:v>Observed / Code-confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="72" customHeight="1">
+      <x:c r="A34" s="120" t="str">
+        <x:v>API origin contract</x:v>
+      </x:c>
+      <x:c r="B34" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C34" s="120" t="str">
+        <x:v>4/4 focused contracts: hostile origins fail before bindings; missing/null/path/malformed origins fail; exact same-origin assistant/feedback succeed without CORS; OPTIONS enforces the same boundary.</x:v>
+      </x:c>
+      <x:c r="D34" s="120" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E34" s="120" t="str">
+        <x:v>Batch 6; Node Worker mock; no external AI or email</x:v>
+      </x:c>
+      <x:c r="F34" s="120" t="str">
+        <x:v>Observed / Code-confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="72" customHeight="1">
+      <x:c r="A35" s="118" t="str">
+        <x:v>npm test — batch 6</x:v>
+      </x:c>
+      <x:c r="B35" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C35" s="118" t="str">
+        <x:v>44/44; 0 failed; 0 skipped</x:v>
+      </x:c>
+      <x:c r="D35" s="118" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E35" s="118" t="str">
+        <x:v>Batch 6; Node test runner</x:v>
+      </x:c>
+      <x:c r="F35" s="118" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="72" customHeight="1">
+      <x:c r="A36" s="120" t="str">
+        <x:v>npm run test:e2e — batch 6</x:v>
+      </x:c>
+      <x:c r="B36" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C36" s="120" t="str">
+        <x:v>Final clean Chromium regression 33/33. The initial sandbox attempt could not bind the local server; the approved rerun executed the application suite and passed.</x:v>
+      </x:c>
+      <x:c r="D36" s="120" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E36" s="120" t="str">
+        <x:v>Batch 6; Chromium; local static server</x:v>
+      </x:c>
+      <x:c r="F36" s="120" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="72" customHeight="1">
+      <x:c r="A37" s="118" t="str">
+        <x:v>Local Wrangler privacy/origin check</x:v>
+      </x:c>
+      <x:c r="B37" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C37" s="118" t="str">
+        <x:v>Root and generated guide served strict self-only CSP. Same-origin preflight returned 204; hostile and missing origins returned 403; allowed malformed feedback reached normal 400 validation. No real AI or email was invoked.</x:v>
+      </x:c>
+      <x:c r="D37" s="118" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E37" s="118" t="str">
+        <x:v>Batch 6; Wrangler local at 127.0.0.1:8799</x:v>
+      </x:c>
+      <x:c r="F37" s="118" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="72" customHeight="1">
+      <x:c r="A38" s="120" t="str">
+        <x:v>Wrangler dry-run — batch 6</x:v>
+      </x:c>
+      <x:c r="B38" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C38" s="120" t="str">
+        <x:v>Wrangler 4.112.0; 110 assets; 201.10 KiB / 52.20 KiB gzip; expected KV, email, AI, rate-limit, and asset bindings.</x:v>
+      </x:c>
+      <x:c r="D38" s="120" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E38" s="120" t="str">
+        <x:v>Batch 6; no deployment performed</x:v>
+      </x:c>
+      <x:c r="F38" s="120" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="72" customHeight="1">
+      <x:c r="A39" s="118" t="str">
+        <x:v>Production privacy/origin recheck</x:v>
+      </x:c>
+      <x:c r="B39" s="140" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="C39" s="118" t="str">
+        <x:v>Production still served the explicit analytics beacon and widened analytics CSP; hostile API preflight returned wildcard CORS. Expected until the local batch is deployed and the Web Analytics site is disabled.</x:v>
+      </x:c>
+      <x:c r="D39" s="118" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E39" s="118" t="str">
+        <x:v>abilityfinder.ca; safe HEAD/OPTIONS/HTML checks; Cloudflare SEA edge</x:v>
+      </x:c>
+      <x:c r="F39" s="118" t="str">
+        <x:v>Observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="72" customHeight="1">
+      <x:c r="A40" s="120" t="str">
+        <x:v>git diff --check — batches 4–6</x:v>
+      </x:c>
+      <x:c r="B40" s="133" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C40" s="120" t="str">
+        <x:v>No whitespace errors.</x:v>
+      </x:c>
+      <x:c r="D40" s="120" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="E40" s="120" t="str">
+        <x:v>Local repository; no commit, push, or deployment performed</x:v>
+      </x:c>
+      <x:c r="F40" s="120" t="str">
         <x:v>Observed</x:v>
       </x:c>
     </x:row>
